--- a/data/trans_orig/P04C05_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04C05_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con refrigeración por aire acondicionado mediante aparatos fijos en la vivienda en 2023</t>
+          <t>Población según si dispone de refrigeración por aire acondicionado mediante aparatos fijos en la vivienda en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71050</t>
+          <t>67930</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130583</t>
+          <t>128216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65011</t>
+          <t>61973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111520</t>
+          <t>106532</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146272</t>
+          <t>143977</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217721</t>
+          <t>219549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>266307</t>
+          <t>269909</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>326070</t>
+          <t>329838</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>200389</t>
+          <t>206051</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>246995</t>
+          <t>249865</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>491787</t>
+          <t>488971</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>563530</t>
+          <t>565656</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64152</t>
+          <t>62362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107835</t>
+          <t>107297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112771</t>
+          <t>112016</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313191</t>
+          <t>308473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>192505</t>
+          <t>189063</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>413438</t>
+          <t>421164</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>14296</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>311689</t>
+          <t>310743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>356002</t>
+          <t>356036</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>195883</t>
+          <t>201459</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>396071</t>
+          <t>396807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>515947</t>
+          <t>507960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>734776</t>
+          <t>738333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103715</t>
+          <t>102739</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143878</t>
+          <t>143947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100390</t>
+          <t>98258</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>156027</t>
+          <t>158158</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>222600</t>
+          <t>221584</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>289478</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>12085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>17732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>386455</t>
+          <t>386086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>427309</t>
+          <t>427770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>428549</t>
+          <t>427461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>486030</t>
+          <t>487379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>824385</t>
+          <t>824688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>894775</t>
+          <t>893888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,44%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68818</t>
+          <t>65363</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>218370</t>
+          <t>217283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132305</t>
+          <t>134113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179115</t>
+          <t>181446</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183235</t>
+          <t>187338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>376698</t>
+          <t>377896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26472</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32842</t>
+          <t>32908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>649149</t>
+          <t>650843</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>811191</t>
+          <t>817606</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>527011</t>
+          <t>523961</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>574173</t>
+          <t>573670</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1197474</t>
+          <t>1194886</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1403056</t>
+          <t>1396299</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>127677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>170588</t>
+          <t>169502</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125227</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156837</t>
+          <t>157780</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>264589</t>
+          <t>265657</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>316581</t>
+          <t>315528</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>20219</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>384256</t>
+          <t>385291</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>426262</t>
+          <t>427264</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>382147</t>
+          <t>380644</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>413538</t>
+          <t>411675</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>775990</t>
+          <t>778370</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>828739</t>
+          <t>828797</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82732</t>
+          <t>83168</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>110734</t>
+          <t>110567</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51925</t>
+          <t>52909</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>189783</t>
+          <t>189693</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114210</t>
+          <t>117644</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>281950</t>
+          <t>283647</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>253820</t>
+          <t>252087</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>281988</t>
+          <t>281505</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>410546</t>
+          <t>411686</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>553952</t>
+          <t>552455</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>683106</t>
+          <t>681611</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>857309</t>
+          <t>855585</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,61%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70701</t>
+          <t>69851</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>94500</t>
+          <t>95181</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>137725</t>
+          <t>139260</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>165082</t>
+          <t>166214</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>215700</t>
+          <t>216740</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>254573</t>
+          <t>255236</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15078</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>184926</t>
+          <t>183788</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>208096</t>
+          <t>208738</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>254949</t>
+          <t>254368</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>283298</t>
+          <t>282490</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>445252</t>
+          <t>444229</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>484227</t>
+          <t>483693</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>617313</t>
+          <t>587270</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>857821</t>
+          <t>860060</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>810917</t>
+          <t>821691</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1115023</t>
+          <t>1121098</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1517268</t>
+          <t>1517165</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1917868</t>
+          <t>1916964</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>27914</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>56234</t>
+          <t>55535</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>23068</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>41465</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>58432</t>
+          <t>57314</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>90684</t>
+          <t>91208</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2555774</t>
+          <t>2552235</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2806529</t>
+          <t>2841414</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2562267</t>
+          <t>2554007</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2873706</t>
+          <t>2859473</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5180703</t>
+          <t>5168614</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5593033</t>
+          <t>5576810</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04C05_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04C05_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>96714</t>
+          <t>103744</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67930</t>
+          <t>77840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128216</t>
+          <t>140322</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>84187</t>
+          <t>100423</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61973</t>
+          <t>77757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106532</t>
+          <t>125001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>180901</t>
+          <t>204167</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>143977</t>
+          <t>166086</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>219549</t>
+          <t>239162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>20520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>301284</t>
+          <t>300491</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269909</t>
+          <t>266221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>329838</t>
+          <t>326548</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>227511</t>
+          <t>256686</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>206051</t>
+          <t>229904</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>249865</t>
+          <t>279489</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>528795</t>
+          <t>557178</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>488971</t>
+          <t>518476</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>565656</t>
+          <t>594490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>83467</t>
+          <t>98689</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62362</t>
+          <t>75781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107297</t>
+          <t>123437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>172146</t>
+          <t>128146</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112016</t>
+          <t>108774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>308473</t>
+          <t>149179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>255614</t>
+          <t>226835</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189063</t>
+          <t>195169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>421164</t>
+          <t>256106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14296</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16967</t>
+          <t>23913</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>334493</t>
+          <t>368237</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>310743</t>
+          <t>343140</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>356036</t>
+          <t>391866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>337061</t>
+          <t>369976</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201459</t>
+          <t>350163</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>396807</t>
+          <t>390153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>671554</t>
+          <t>738213</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>507960</t>
+          <t>707550</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>738333</t>
+          <t>770458</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>510969</t>
+          <t>500662</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>510969</t>
+          <t>500662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>510969</t>
+          <t>500662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>934516</t>
+          <t>977552</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>934516</t>
+          <t>977552</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>934516</t>
+          <t>977552</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122833</t>
+          <t>161362</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102739</t>
+          <t>141535</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143947</t>
+          <t>186693</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>136268</t>
+          <t>164868</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98258</t>
+          <t>146565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158158</t>
+          <t>183172</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>259101</t>
+          <t>326230</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>221584</t>
+          <t>295144</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>289478</t>
+          <t>355265</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17732</t>
+          <t>20228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>407416</t>
+          <t>451575</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>386086</t>
+          <t>426397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>427770</t>
+          <t>473076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>448940</t>
+          <t>449336</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>427461</t>
+          <t>430286</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>487379</t>
+          <t>467393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>856356</t>
+          <t>900911</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>824688</t>
+          <t>870972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>893888</t>
+          <t>931247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>75,17%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>535154</t>
+          <t>618573</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>535154</t>
+          <t>618573</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>535154</t>
+          <t>618573</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>590118</t>
+          <t>620352</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>590118</t>
+          <t>620352</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>590118</t>
+          <t>620352</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1125272</t>
+          <t>1238925</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1125272</t>
+          <t>1238925</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1125272</t>
+          <t>1238925</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>149518</t>
+          <t>177476</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65363</t>
+          <t>152474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217283</t>
+          <t>203802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>158701</t>
+          <t>167070</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134113</t>
+          <t>148988</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181446</t>
+          <t>186345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>308219</t>
+          <t>344547</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>187338</t>
+          <t>311481</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>377896</t>
+          <t>373053</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14636</t>
+          <t>16578</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>27774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11086</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>20696</t>
+          <t>24242</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32908</t>
+          <t>35347</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>723632</t>
+          <t>506563</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>650843</t>
+          <t>480989</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>817606</t>
+          <t>531898</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547463</t>
+          <t>561454</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>523961</t>
+          <t>542004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>573670</t>
+          <t>579615</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1271096</t>
+          <t>1068017</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1194886</t>
+          <t>1036713</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1396299</t>
+          <t>1100867</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712224</t>
+          <t>736188</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712224</t>
+          <t>736188</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712224</t>
+          <t>736188</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1600011</t>
+          <t>1436805</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1600011</t>
+          <t>1436805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1600011</t>
+          <t>1436805</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>148199</t>
+          <t>163876</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>127677</t>
+          <t>142677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>169502</t>
+          <t>184593</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>141500</t>
+          <t>159714</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>141155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>157780</t>
+          <t>176873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>289699</t>
+          <t>323591</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>265657</t>
+          <t>296142</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>315528</t>
+          <t>349682</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>17164</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>407069</t>
+          <t>436111</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>385291</t>
+          <t>414557</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>427264</t>
+          <t>457059</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>397457</t>
+          <t>439560</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>380644</t>
+          <t>422143</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>411675</t>
+          <t>457189</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>804526</t>
+          <t>875670</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>778370</t>
+          <t>849056</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>828797</t>
+          <t>905457</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>560260</t>
+          <t>608404</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560260</t>
+          <t>608404</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>560260</t>
+          <t>608404</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>546041</t>
+          <t>606773</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>546041</t>
+          <t>606773</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>546041</t>
+          <t>606773</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1106301</t>
+          <t>1215177</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1106301</t>
+          <t>1215177</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1106301</t>
+          <t>1215177</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>95991</t>
+          <t>109517</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83168</t>
+          <t>94820</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>110567</t>
+          <t>124461</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>121135</t>
+          <t>132906</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52909</t>
+          <t>118880</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>189693</t>
+          <t>147454</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>217126</t>
+          <t>242423</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>117644</t>
+          <t>221194</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>283647</t>
+          <t>265368</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>267687</t>
+          <t>292541</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>252087</t>
+          <t>277409</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>281505</t>
+          <t>307778</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>482086</t>
+          <t>300775</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>411686</t>
+          <t>286657</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>552455</t>
+          <t>315228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>749772</t>
+          <t>593317</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>681611</t>
+          <t>570494</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>855585</t>
+          <t>613725</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>72,52%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>82665</t>
+          <t>90501</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>69851</t>
+          <t>77460</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>95181</t>
+          <t>104439</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>151726</t>
+          <t>163218</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>139260</t>
+          <t>148932</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>166214</t>
+          <t>180232</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>234391</t>
+          <t>253718</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>216740</t>
+          <t>234103</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>255236</t>
+          <t>274968</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3687,17 +3687,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>196303</t>
+          <t>215338</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>183788</t>
+          <t>201366</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>208738</t>
+          <t>228063</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>268638</t>
+          <t>295241</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>254368</t>
+          <t>279589</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>282490</t>
+          <t>309796</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>464941</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>444229</t>
+          <t>489666</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>483693</t>
+          <t>531402</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>779388</t>
+          <t>905166</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>587270</t>
+          <t>846007</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>860060</t>
+          <t>964055</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>965663</t>
+          <t>1016345</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>821691</t>
+          <t>965689</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1121098</t>
+          <t>1061901</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1745051</t>
+          <t>1921511</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1517165</t>
+          <t>1850449</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1916964</t>
+          <t>2001015</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>40386</t>
+          <t>53533</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>40911</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>55535</t>
+          <t>71789</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>31932</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>23068</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>41465</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>94422</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>57314</t>
+          <t>77379</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>91208</t>
+          <t>116483</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2637885</t>
+          <t>2570857</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2552235</t>
+          <t>2511714</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2841414</t>
+          <t>2629919</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2709156</t>
+          <t>2673028</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2554007</t>
+          <t>2624425</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2859473</t>
+          <t>2724674</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5347041</t>
+          <t>5243886</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5168614</t>
+          <t>5162112</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5576810</t>
+          <t>5316237</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3457659</t>
+          <t>3529556</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3457659</t>
+          <t>3529556</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3457659</t>
+          <t>3529556</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3706751</t>
+          <t>3730262</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3706751</t>
+          <t>3730262</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3706751</t>
+          <t>3730262</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7164410</t>
+          <t>7259818</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7164410</t>
+          <t>7259818</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7164410</t>
+          <t>7259818</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
